--- a/output/pdf_financials_xlsx/PSD.xlsx
+++ b/output/pdf_financials_xlsx/PSD.xlsx
@@ -1081,28 +1081,28 @@
         <v>-0.184</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.249</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.296</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.473</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.103</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -2108,28 +2108,28 @@
         <v>7.138</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>36.486</v>
+        <v>36.735</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-25.302</v>
+        <v>-25.264</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.606</v>
+        <v>4.62</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.334</v>
+        <v>-6.333</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-10.357</v>
+        <v>-10.306</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>20.666</v>
+        <v>20.962</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.408</v>
+        <v>-1.935</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.185</v>
+        <v>-2.082</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2240,28 +2240,28 @@
         <v>7.387</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>36.78</v>
+        <v>37.029</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-24.984</v>
+        <v>-24.946</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.854</v>
+        <v>4.868</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.149</v>
+        <v>-6.148</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-10.213</v>
+        <v>-10.162</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>20.784</v>
+        <v>21.08</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.337</v>
+        <v>-1.864</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.437</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2309,19 +2309,19 @@
         <v>14.35093445234487</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>42.59261403772886</v>
+        <v>42.88096533994187</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-61.67670583588427</v>
+        <v>-61.58289720549027</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>13.58028145371122</v>
+        <v>13.61944996223037</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-25.16575263976426</v>
+        <v>-25.16165998199231</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-71.22532952088709</v>
+        <v>-70.8696561824395</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-22.93875147232038</v>
+        <v>-18.29603455045151</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-6.375491616642518</v>
+        <v>-5.949078865659284</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -51024,7 +51024,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -52642,7 +52642,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">

--- a/output/pdf_financials_xlsx/PSD.xlsx
+++ b/output/pdf_financials_xlsx/PSD.xlsx
@@ -1138,25 +1138,25 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.389</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-3.972</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-2.009</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.383</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.875</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.494</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.124</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>-0</v>
@@ -2105,22 +2105,22 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.138</v>
+        <v>11.11</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>36.735</v>
+        <v>38.744</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-25.264</v>
+        <v>-23.881</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.62</v>
+        <v>5.495</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.333</v>
+        <v>-5.839</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-10.306</v>
+        <v>-10.182</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>20.962</v>
@@ -2237,22 +2237,22 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.387</v>
+        <v>11.359</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>37.029</v>
+        <v>39.038</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-24.946</v>
+        <v>-23.563</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.868</v>
+        <v>5.743</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.148</v>
+        <v>-5.654</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-10.162</v>
+        <v>-10.038</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>21.08</v>
@@ -2306,22 +2306,22 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14.35093445234487</v>
+        <v>22.06745152892723</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>42.88096533994187</v>
+        <v>45.20746239273679</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-61.58289720549027</v>
+        <v>-58.16875678878246</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>13.61944996223037</v>
+        <v>16.06748174467728</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-25.16165998199231</v>
+        <v>-23.13988704264549</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-70.8696561824395</v>
+        <v>-70.00488179091987</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -51118,7 +51118,11 @@
           <t>Net financing costs</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -52734,7 +52738,11 @@
           <t>Net financing costs</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -54916,7 +54924,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
